--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5125,6 +5125,114 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111946116</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90441</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Knoppenborg, Knoppenborg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>395690</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6849834</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90441</v>
+        <v>90520</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90519</v>
+        <v>90522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90522</v>
+        <v>90548</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90548</v>
+        <v>90549</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90549</v>
+        <v>90550</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 30220-2023 artfynd.xlsx
+++ b/artfynd/A 30220-2023 artfynd.xlsx
@@ -5130,7 +5130,7 @@
         <v>111946116</v>
       </c>
       <c r="B40" t="n">
-        <v>90550</v>
+        <v>90552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
